--- a/docs/assessment/templates/sharepoint-admin-checklist.xlsx
+++ b/docs/assessment/templates/sharepoint-admin-checklist.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Microsoft 365 Copilot Optimization Assessment has been run and infrastructure findings (network, update channel, app compatibility) have been reviewed and addressed; Office update channel compliance has been measured and meets the target for the organization's governance level (&gt;80% Baseline / &gt;95% Recommended / 100% policy-enforced for Regulated); DSPM for AI reports have been generated and reviewed by designated personnel within the past 30 days; SharePoint Data Access Governance reports have been run for all in-scope site collections; Content Explorer analysis has identified and documented the location and volume of sensitive information types across M365 workloads; Permission audit has been completed for all workloads at the appropriate governance level (SharePoint minimum; all workloads for Regulated); Readiness scoring model has been applied and current scores documented; Gap analysis comparing current state to target governance level has been completed; Remediation plan with prioritized actions and timelines has been developed and approved by appropriate stakeholders; Readiness assessment findings have been presented to IT leadership and compliance (Baseline) or documented in regulatory examination file (Regulated); Assessment artifacts (reports, exports, scoring worksheets) are retained per the organization's document retention policy; Re-assessment cadence has been established (quarterly recommended; semi-annual minimum)</t>
+          <t>Readiness assessment report with date, scope, and findings summary; Remediation backlog with named owners and target dates; Data classification coverage percentage across Copilot-grounded sites; Executive sign-off on readiness findings and go/no-go decision</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Tenant setting screenshot showing IsRestrictedSPSearchEnabled = $true; Current allow-list site URLs (≤100) with business owner per site; RCD exception register (sites surgically excluded outside the allow-list model); Documented exit plan / transition target date to long-term Purview+SAM governance</t>
+          <t>PowerShell output showing Get-SPOTenantRestrictedSearchMode returns Enabled; Current allow-list site URLs (≤100) with business owner per site; RCD exception register for targeted site-level exclusions; Documented exit plan / transition target date to long-term Purview+SAM governance</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>SharePoint site permissions have been audited for EEEU and "Everyone" access across all in-scope sites; All EEEU permissions on sites containing sensitive data have been remediated (replaced with specific security groups); OneDrive sharing configuration has been reviewed and overly broad sharing links addressed (Recommended and Regulated levels); Exchange mailbox delegation permissions have been audited for appropriateness (Recommended and Regulated levels); Teams membership has been reviewed for overly broad access patterns (Recommended and Regulated levels); Graph API permissions for applications and service principals have been audited (Regulated level); Purview Data Security AI Viewer role assigned to compliance team (Baseline and above); Purview Data Security AI Content Viewer role assigned to investigation team with documented authorization (Recommended and Regulated levels); AI Administrator role assigned to Copilot governance lead (Recommended and Regulated levels); Formal role assignment policy established for all AI-prefixed roles with quarterly access review (Regulated level); Permission audit findings are documented with risk classifications and remediation actions; Remediation actions are verified through re-audit with documentation of before/after states; Recurring permission audit cadence is established (quarterly / monthly for high-sensitivity per governance level); Permission audit reports and remediation logs are retained and accessible for regulatory examination</t>
+          <t>Permission audit report with date, scope, and findings; List of sites with Everyone/EEEU sharing and remediation status; Least-privilege evidence for Copilot-grounded knowledge sources; Audit cadence documentation (90-day cycle)</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>SAM licensing status has been evaluated and confirmed (included with Copilot licenses; documented); DAG reports have been generated and reviewed within the past 30 days; Site permissions snapshot report has been generated as a pre-deployment baseline (documented with date); DAG report findings have been triaged and assigned for remediation; RCD is enabled for sites containing highly sensitive data that should not be in Copilot scope (Recommended and Regulated levels); RAC is enabled for sites containing NPI or MNPI with documented security group membership (Recommended and Regulated levels); Site access reviews have been initiated for sites with broadest sharing (Recommended and Regulated levels); Site access review completion rates are tracked and reported; Site lifecycle management is configured with appropriate inactivity thresholds (Recommended and Regulated levels); DAG reporting cadence is established (monthly minimum for Recommended; continuous for Regulated); SAM configuration (RCD, RAC, lifecycle policies) is documented in the organization's Copilot governance documentation; SAM governance features and their outputs are included in regulatory examination readiness materials (Regulated level)</t>
+          <t>SAM license confirmation and feature activation status; RAC/RCD configuration for high-risk Copilot-grounded sites; Site lifecycle management policy with review cadence; Content Management Assessment report (if available)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Comprehensive inventory of active SharePoint sites has been completed with key metadata captured; Comprehensive inventory of Teams has been completed with key metadata captured; Orphaned and stale sites and Teams have been identified and documented; Naming conventions have been reviewed and gaps identified for in-scope sites and Teams; Architecture assessment scoring has been completed for each review dimension; Stale and orphaned sites have been remediated (archived or deleted) or have documented justification for retention; Hub site architecture and site classification coverage has been assessed (Recommended and Regulated levels); Content type and metadata usage has been assessed for top sites (Recommended and Regulated levels); Information architecture improvement roadmap has been created with prioritized actions and timelines; Information architecture standards document exists and is being applied to new site and Teams creation (Regulated level)</t>
+          <t>IA review report with date, scope, and grounding suitability findings; Hub-association map for Copilot-grounded sites; Content-type and metadata taxonomy alignment documentation</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Site-level DAG baseline has been established (Control 1.7) before item-level scanning commences; DSPM oversharing assessment has been run (Control 1.2) and remediated before item-level scoping; Item-level scanning has been deployed and executed on all in-scope sites per governance level; Risk scoring thresholds have been configured and documented; All CRITICAL uniquely permissioned items have been remediated or have documented exception approvals; All HIGH uniquely permissioned items have remediation plans with defined timelines; Approval workflow is operational with documented approvals for CRITICAL and HIGH item remediations; Recurring scan schedule is configured per governance level (quarterly / monthly / weekly); Scan results and remediation records are retained per organization retention policy (7 years for regulated entities per SEC 17a-4); Item-level scan reports are included in regulatory examination evidence package (Regulated level)</t>
+          <t>Item-level permission scan report with scan date and scope; List of items with overly broad permissions and remediation status; Documented scan cadence (weekly, monthly, quarterly); Remediation backlog with named owners</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Initial permissions baseline has been established for all in-scope sites per governance level; Baseline has been reviewed and approved by site owners and Compliance Lead; Drift scanning is deployed and running at the configured cadence (quarterly / monthly / weekly); Drift classification thresholds are configured and documented; All CRITICAL drift findings have been remediated or reverted within SLA (4 hours); All HIGH drift findings have been remediated within SLA (24 hours); Approval workflow is operational for drift remediation decisions; Auto-revert policy is configured and tested (Regulated level); Evidence retention is configured with 7-year retention for regulated entities per SEC 17a-4; Drift detection reports are integrated into compliance reporting and accessible for regulatory examination; Quarterly baseline accuracy review has been conducted (Regulated level); Drift detection findings are correlated with DSPM oversharing assessments (Control 1.2) for comprehensive access risk visibility</t>
+          <t>Permissions drift detection report or alert log; Reconciliation records for detected drift events; Monitoring cadence documentation; RAC or site lifecycle management configuration evidence</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Creation policy scoped: Verify the Cloud Policy for Create and view Copilot Pages and Copilot Notebooks is applied to the intended users or groups only.; Code preview decision documented: Confirm the code preview policy is either disabled or enabled with documented business justification.; Storage visibility confirmed: Verify administrators can identify user-owned SharePoint Embedded containers for Pages/Notebooks.; Sharing posture validated: Create a test Page and confirm sharing behavior matches the firm's approved model.; Sensitivity and DLP controls tested: Confirm Pages content can be labeled and that DLP policies detect test sensitive data.; Retention coverage verified: Confirm relevant retention policies covering All SharePoint Sites apply to Pages/Notebooks content.; eDiscovery search tested: Run an eDiscovery test for Pages content and verify results can be reviewed and exported.; Legal hold workflow documented: Confirm the team can manually target the user's container for hold when required.; IB exception handling documented: Verify high-segmentation populations are either excluded from Pages/Notebooks or have compensating controls documented.; Offboarding procedure updated: Confirm user departure procedures address preservation of Pages/Notebooks content before cleanup windows expire.</t>
+          <t>Pages sharing policy configuration; Sensitivity label enforcement for Pages content; External sharing restriction evidence; Sharing activity audit log entries for Pages</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Org-Wide Sharing Level: Verify the org-wide external sharing level is set to "Existing guests only" or more restrictive; Anonymous Links Disabled: Confirm "Anyone" links are disabled org-wide; Sensitive Site Sharing: Verify that sites containing client data, regulatory content, and executive materials have sharing set to "Disabled"; Guest Copilot Licensing: Confirm no guest accounts have Microsoft 365 Copilot licenses assigned; Guest Invitation Restriction: Attempt to invite a guest as a standard user — verify the invitation is blocked; Access Reviews Active: Confirm Entra ID Access Reviews for guest accounts are configured and running on schedule; Guest Account Expiration: Verify guest account expiration is configured and functioning; Domain Restrictions: Verify that allowed domain lists are configured and only approved domains can receive sharing invitations; Audit Logging: Confirm external sharing events appear in the Unified Audit Log and are monitored; Policy Documentation: Verify that external sharing policies are documented, approved by compliance, and reviewed annually</t>
+          <t>Tenant and site-level sharing policy configuration; Approved external domain list (if domain restriction is used); Entra access review configuration for guest accounts; Sharing activity monitoring report from audit logs</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/sharepoint-admin-checklist.xlsx
+++ b/docs/assessment/templates/sharepoint-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: SharePoint Admin  |  FSI Copilot Governance Framework v1.4  |  10 controls</t>
+          <t>Role: SharePoint Admin  |  FSI Copilot Governance Framework v1.8  |  10 controls</t>
         </is>
       </c>
     </row>

--- a/docs/assessment/templates/sharepoint-admin-checklist.xlsx
+++ b/docs/assessment/templates/sharepoint-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: SharePoint Admin  |  FSI Copilot Governance Framework v1.8  |  10 controls</t>
+          <t>Role: SharePoint Admin  |  FSI Copilot Governance Framework v1.8.0  |  10 controls</t>
         </is>
       </c>
     </row>

--- a/docs/assessment/templates/sharepoint-admin-checklist.xlsx
+++ b/docs/assessment/templates/sharepoint-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: SharePoint Admin  |  FSI Copilot Governance Framework v1.4  |  10 controls</t>
+          <t>Role: SharePoint Admin  |  FSI Copilot Governance Framework v1.8.0  |  10 controls</t>
         </is>
       </c>
     </row>

--- a/docs/assessment/templates/sharepoint-admin-checklist.xlsx
+++ b/docs/assessment/templates/sharepoint-admin-checklist.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>SharePoint Advanced Management Readiness for Copilot</t>
+          <t>Are SharePoint Advanced Management controls (RCD, RAC, site lifecycle) enabled and configured for Copilot-grounded sites?</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Copilot Pages Security and Sharing Controls</t>
+          <t>Are Copilot Pages security controls configured to prevent unauthorized sharing and reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">

--- a/docs/assessment/templates/sharepoint-admin-checklist.xlsx
+++ b/docs/assessment/templates/sharepoint-admin-checklist.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Tenant and site-level sharing policy configuration; Approved external domain list (if domain restriction is used); Entra access review configuration for guest accounts; Sharing activity monitoring report from audit logs</t>
+          <t>Tenant and site-level sharing policy configuration; Approved external domain list (if domain restriction is used); SharePoint/OneDrive guest-access expiration settings, policy enablement date, and overrides; Microsoft 365 group, security group, and Teams access-path reconciliation for guests; Entra access review scope and post-review actions for guest accounts; Sharing activity monitoring report from audit logs</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/sharepoint-admin-checklist.xlsx
+++ b/docs/assessment/templates/sharepoint-admin-checklist.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Tenant and site-level sharing policy configuration; Approved external domain list (if domain restriction is used); SharePoint/OneDrive guest-access expiration settings, policy enablement date, and overrides; Microsoft 365 group, security group, and Teams access-path reconciliation for guests; Entra access review scope and post-review actions for guest accounts; Sharing activity monitoring report from audit logs</t>
+          <t>Tenant and site-level sharing policy configuration; Approved external domain list (if domain restriction is used); SharePoint/OneDrive guest-access expiration settings, policy enablement date, and overrides; Microsoft 365 group, security group, and Teams access-path reconciliation for guests; Resource-scoped Entra access review scope and results, plus separate guest-lifecycle review evidence for any tenant-wide account action; Sharing activity monitoring report from audit logs</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
